--- a/Matriz_Normativa_IA_Educacion_LATAM.xlsx
+++ b/Matriz_Normativa_IA_Educacion_LATAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/a00834778_tec_mx/Documents/Desktop/Carlos Auquilla/Proyectos/GENIAL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="630" documentId="13_ncr:1_{65400818-7CE5-0644-BE68-1BD2DD50F50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06735268-8396-471A-B5B8-A2F6333F3657}"/>
+  <xr:revisionPtr revIDLastSave="740" documentId="13_ncr:1_{65400818-7CE5-0644-BE68-1BD2DD50F50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4D682CE-5798-4D54-AA06-6219B1181BE7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro de Normativa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="339">
   <si>
     <t>Investigador</t>
   </si>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>Dedicación del Texto</t>
-  </si>
-  <si>
-    <t>Fecha de Publicación</t>
   </si>
   <si>
     <t>URL Oficial</t>
@@ -980,16 +977,98 @@
   </si>
   <si>
     <t>Carlos Auquilla</t>
+  </si>
+  <si>
+    <t>Desafíos normativos en la era digital: Desarrollo de IA y protección de datos</t>
+  </si>
+  <si>
+    <t>https://entorno.udlap.mx/wp-content/uploads/2025/09/Desafios-normativos-IA-Entorno24.pdf</t>
+  </si>
+  <si>
+    <t>UDLAP</t>
+  </si>
+  <si>
+    <t>18/06/2025</t>
+  </si>
+  <si>
+    <t>Análisis de los desafíos normativos en la implementación de IA y en la protección de datos.</t>
+  </si>
+  <si>
+    <t>Reglamentos de Estudios Profesionales 2025</t>
+  </si>
+  <si>
+    <t>ITAM</t>
+  </si>
+  <si>
+    <t>https://escolar.itam.mx/documentos/reg_licenciatura.pdf</t>
+  </si>
+  <si>
+    <t>Se estipula que los miembros de la comunidad se comprometen a utilizar las herramientas de inteligencia artificial de acuerdo con las recomendaciones y lineamientos que el Instituto expida al respecto.</t>
+  </si>
+  <si>
+    <t>Recomendaciones éticas sobre el uso de la inteligencia artificial (IA) en educación superior: una revisión sistemática</t>
+  </si>
+  <si>
+    <t>https://www.google.com.mx/url?sa=t&amp;source=web&amp;rct=j&amp;opi=89978449&amp;url=https://dialogossobreeducacion.cucsh.udg.mx/index.php/DSE/article/view/1743/1499&amp;ved=2ahUKEwjz9uac26qUAxXtQTABHWEoDL4QFnoECBgQAQ&amp;usg=AOvVaw14DVx1Hkx2ZA_uXZVfbZug</t>
+  </si>
+  <si>
+    <t>15/08/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se establecen los siguientes segmentos: recomendaciones para instituciones, recomendaciones para profesorado y para alumnado. </t>
+  </si>
+  <si>
+    <t>CEDIM</t>
+  </si>
+  <si>
+    <t>Manual del Estudiante</t>
+  </si>
+  <si>
+    <t>https://www.primeringreso.cedim.edu.mx/wp-content/uploads/2023/12/Manual_del_Estudiante_CEDIM.pdf</t>
+  </si>
+  <si>
+    <t>Documento institucional reglamentario. Estipula que se debe citar el uso de la inteligencia artificial en todo tipo de trabajo.</t>
+  </si>
+  <si>
+    <t>Iniciativa con Proyecto de Decreto por el que se expide la Ley Federal para el desarrollo ético, soberano e inclusivo de la Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>Honorable Congreso de la Unión</t>
+  </si>
+  <si>
+    <t>30/04/2025</t>
+  </si>
+  <si>
+    <t>http://sil.gobernacion.gob.mx/Archivos/Documentos/2025/04/asun_4896460_20250430_1747757009.pdf</t>
+  </si>
+  <si>
+    <t>Establece un marco normativo para el desarrollo ético de la IA, abordando su impacto en 'educación', 'derechos' y 'oportunidades'. Promueve un enfoque 'soberano' e 'inclusivo' en la implementación de tecnologías de IA.</t>
+  </si>
+  <si>
+    <t>Lineamientos para presentar propuestas de experiencias en evaluación del y para el aprendizaje con inteligencia artificial</t>
+  </si>
+  <si>
+    <t>01/04/2026</t>
+  </si>
+  <si>
+    <t>https://www.cee.unam.mx/wp-content/uploads/2026/04/EvaluaFEST_2026_Lineamientos_para_presentar_propuestas.pdf</t>
+  </si>
+  <si>
+    <t>Establece los 'Lineamientos para presentar propuestas de experiencias en evaluación del y para el aprendizaje con inteligencia artificial'. Define criterios como 'innovación en el uso de la IA' y ejes temáticos relacionados con la evaluación educativa.</t>
+  </si>
+  <si>
+    <t>Fecha de Publicación DD/MM/YY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1019,8 +1098,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1039,8 +1122,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1063,11 +1151,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1077,19 +1180,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1425,13 +1531,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
@@ -1443,2598 +1549,2739 @@
         <v>6</v>
       </c>
       <c r="J1" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="M1" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2" s="6">
         <f>DATE(2026,2,11)</f>
         <v>46064</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J3" s="6">
         <v>45742</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="J4" s="6">
         <v>45694</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="J5" s="6">
         <v>45292</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="J6" s="6">
         <v>45961</v>
       </c>
       <c r="K6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="L6" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="M6" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J7" s="6">
         <v>46051</v>
       </c>
       <c r="K7" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="M7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="H8" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J8" s="6">
         <v>46038</v>
       </c>
       <c r="K8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="M8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J9" s="6">
         <v>46127</v>
       </c>
       <c r="K9" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="M9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J10" s="6">
         <v>46127</v>
       </c>
       <c r="K10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="M10" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="J11" s="6">
         <v>45352</v>
       </c>
       <c r="K11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="M11" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J12" s="6">
         <v>45778</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="G13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="J13" s="6">
         <v>45809</v>
       </c>
       <c r="K13" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="L13" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="M13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="G14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J14" s="6">
         <v>45992</v>
       </c>
       <c r="K14" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="M14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="G15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="J15" s="6">
         <v>45778</v>
       </c>
       <c r="K15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="M15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="G16" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J16" s="6">
         <v>45778</v>
       </c>
       <c r="K16" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L16" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="M16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="G17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="J17" s="6">
         <v>45778</v>
       </c>
       <c r="K17" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L17" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="L17" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="M17" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="K19" s="3" t="s">
+      <c r="L19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="L19" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="M19" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="G21" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J21" s="6">
         <v>45015</v>
       </c>
       <c r="K21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="L21" t="s">
         <v>140</v>
       </c>
-      <c r="L21" t="s">
-        <v>141</v>
-      </c>
       <c r="M21" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="G22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="J22" s="6">
         <v>45292</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="G23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="J23" s="6">
         <v>45215</v>
       </c>
       <c r="K23" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L23" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="M23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J24" s="6">
         <v>45778</v>
       </c>
       <c r="K24" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="M24" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="G25" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="J25" s="6">
         <v>45678</v>
       </c>
       <c r="K25" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="L25" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="M25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="J26" s="6">
         <v>45931</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J27" s="6">
         <v>45835</v>
       </c>
       <c r="K27" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="M27" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J28" s="6">
         <v>45689</v>
       </c>
       <c r="K28" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="L28" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="L28" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="M28" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G34" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J34" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G44" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J44" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G46" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J46" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F54" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="K54" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="L54" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C63" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="3"/>
-      <c r="M64" s="3"/>
+      <c r="C64" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
+      <c r="C65" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3"/>
-      <c r="M66" s="3"/>
+      <c r="C66" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" s="6">
+        <v>45078</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
+      <c r="C67" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="3"/>
-      <c r="M68" s="3"/>
+      <c r="C68" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J68" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
@@ -4139,25 +4386,25 @@
           <x14:formula1>
             <xm:f>'Tipo de norma'!$A$1:$A$10</xm:f>
           </x14:formula1>
-          <xm:sqref>D64:D1048576 D2:D62</xm:sqref>
+          <xm:sqref>D2:D1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{EF828923-8993-5646-A9D3-B4E6E4049B2E}">
           <x14:formula1>
             <xm:f>Estado!$A$1:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>E64:E1048576 E2:E62</xm:sqref>
+          <xm:sqref>E2:E1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{010CCE2F-A20E-E249-89B6-2FD5F86ADDCB}">
           <x14:formula1>
             <xm:f>Dominio!$A$1:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G64:G1048576 G3:G62</xm:sqref>
+          <xm:sqref>G3:G1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E31F6FF8-8A6C-5643-A155-4F7B3EA2A96D}">
           <x14:formula1>
             <xm:f>'Dedicacion del texto'!$A$1:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>I64:I1048576 I2:I62</xm:sqref>
+          <xm:sqref>I2:I1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{78262786-E61E-8940-BCEE-286BD25672E3}">
           <x14:formula1>
@@ -4193,167 +4440,167 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -4369,52 +4616,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -4433,17 +4680,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4459,27 +4706,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4495,12 +4742,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -4519,22 +4766,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -4550,12 +4797,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Matriz_Normativa_IA_Educacion_LATAM.xlsx
+++ b/Matriz_Normativa_IA_Educacion_LATAM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/a00834778_tec_mx/Documents/Desktop/Carlos Auquilla/Proyectos/GENIAL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/a00834778_tec_mx/Documents/Desktop/Carlos Auquilla/Proyectos/GENIAL/GENIAL_dev/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="740" documentId="13_ncr:1_{65400818-7CE5-0644-BE68-1BD2DD50F50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4D682CE-5798-4D54-AA06-6219B1181BE7}"/>
+  <xr:revisionPtr revIDLastSave="761" documentId="13_ncr:1_{65400818-7CE5-0644-BE68-1BD2DD50F50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9CF101A-5057-4805-8E87-E70B70C1C1B1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="422">
   <si>
     <t>Investigador</t>
   </si>
@@ -1058,6 +1058,256 @@
   </si>
   <si>
     <t>Fecha de Publicación DD/MM/YY</t>
+  </si>
+  <si>
+    <t>Lineamientos Éticos para el Uso Responsable de la Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>APA 7 - Universidad IEU</t>
+  </si>
+  <si>
+    <t>No Indica</t>
+  </si>
+  <si>
+    <t>Política sobre el uso de inteligencia artificial (IA)</t>
+  </si>
+  <si>
+    <t>Reglamento – Tecnológico Nacional de México Lázaro Cárdenas</t>
+  </si>
+  <si>
+    <t>Código de Ética del IPN</t>
+  </si>
+  <si>
+    <t>Ingeniería, ética y sociedad</t>
+  </si>
+  <si>
+    <t>Lineamientos sobre el uso apropiado de la IA en la UPAEP</t>
+  </si>
+  <si>
+    <t>Lineamientos para la implementación de la Inteligencia Artificial Generativa</t>
+  </si>
+  <si>
+    <t>Guía de uso de inteligencia artificial generativa en la evaluación educativa en Licenciatura</t>
+  </si>
+  <si>
+    <t>Una aproximación al marco jurídico de la Inteligencia Artificial en México</t>
+  </si>
+  <si>
+    <t>Criterios sobre el uso de herramientas de inteligencia artificial en el ámbito académico</t>
+  </si>
+  <si>
+    <t>Mapa Curricular, LICENCIATURA EN INGENIERÍA EN TECNOLOGÍAS DE LA INFORMACIÓN E
+INNOVACIÓN DIGITAL</t>
+  </si>
+  <si>
+    <t>Propiedad intelectual y uso de Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>Primer aviso de Convocatoria</t>
+  </si>
+  <si>
+    <t>Reglamento Academico DIES</t>
+  </si>
+  <si>
+    <t>Lineamientos para el Uso Ético y Responsable de la Inteligencia Artificial en el Ámbito Académico</t>
+  </si>
+  <si>
+    <t>Normativa sobre el uso de la inteligencia artificial generativa en los programas de posgrado en educación</t>
+  </si>
+  <si>
+    <t>Acuerdo Rectoral para la Creación del CCOIA-UNAM</t>
+  </si>
+  <si>
+    <t>Benemérita Universidad Autónoma de Chiapas</t>
+  </si>
+  <si>
+    <t>Universidad IEU</t>
+  </si>
+  <si>
+    <t>RETEE</t>
+  </si>
+  <si>
+    <t>Tecnológico Nacional de México Lázaro Cárdenas</t>
+  </si>
+  <si>
+    <t>Instituto Politécnico Nacional</t>
+  </si>
+  <si>
+    <t>UPAEP</t>
+  </si>
+  <si>
+    <t>Universidad de Colima</t>
+  </si>
+  <si>
+    <t>IBERO</t>
+  </si>
+  <si>
+    <t>Universidad Tecnológica de México</t>
+  </si>
+  <si>
+    <t>Suprema Corte de Justicia de la Nación</t>
+  </si>
+  <si>
+    <t>Secretaría de Ciencia, Humanidades, Tecnología e Innovación</t>
+  </si>
+  <si>
+    <t>DIES</t>
+  </si>
+  <si>
+    <t>05/05/2026</t>
+  </si>
+  <si>
+    <t>12/10/2018</t>
+  </si>
+  <si>
+    <t>01/01/2020</t>
+  </si>
+  <si>
+    <t>01/09/2024</t>
+  </si>
+  <si>
+    <t>https://www.unach.mx/images/documentos/legislacion/Lineamientos-ticos-para-el-uso-responsable-de-la-IA.pdf</t>
+  </si>
+  <si>
+    <t>https://media.ieu.edu.mx/supportFiles/apa/manualCriteriosEditoriales_APA6.pdf</t>
+  </si>
+  <si>
+    <t>http://repositorio.cetys.mx:8080/bitstream/60000/1856/1/GUIA+EN+INTELIGENCIA+ARTIFICIAL.pdf</t>
+  </si>
+  <si>
+    <t>https://cuaieed.unam.mx/descargas/recomendaciones-uso-iagen-docencia-unam-2023.pdf</t>
+  </si>
+  <si>
+    <t>https://aguascalientes.gob.mx/IAPAM/IRC/Publicaciones/1.C�DIGO+DE+CONDUCTA.pdf</t>
+  </si>
+  <si>
+    <t>https://revistas.uaz.edu.mx/index.php/RETEE/inteligenciaartificial</t>
+  </si>
+  <si>
+    <t>https://lcardenas.itlac.mx/reglamento/</t>
+  </si>
+  <si>
+    <t>https://www.ipn.mx/assets/files/normatividad/docs/reglamentos/ce-ipn.pdf</t>
+  </si>
+  <si>
+    <t>https://www.escom.ipn.mx/docs/oferta/uaIIA2020/ingenieriaEticaSociedad_IIA2020.pdf</t>
+  </si>
+  <si>
+    <t>https://upaep.mx/estudiantes/correodeldia/comunicados/12909-habilitacirn-de-la-herramienta-oficial-de-inteligencia-artificial--gemini-ia</t>
+  </si>
+  <si>
+    <t>https://elcomentario.ucol.mx/?p=155176</t>
+  </si>
+  <si>
+    <t>https://www.cee.unam.mx/?sdm_process_download=1&amp;download_id=3088</t>
+  </si>
+  <si>
+    <t>https://www.rcs.cic.ipn.mx/2025_154_6/Una%20aproximacion%20al%20marco%20juridico%20de%20la%20Inteligencia%20Artificial%20en%20Mexico.pdf</t>
+  </si>
+  <si>
+    <t>https://www.iberoleon.mx/images/portal/docs/criterios-sobre-el-uso-de-herramientas-de-IA-en-el-ambito-academico.pdf</t>
+  </si>
+  <si>
+    <t>https://utma.edu.mx/images/LIC_EN_ING_EN_TI_E_ID_INTELIGENCIA_ARTIFICIALpdf.pdf</t>
+  </si>
+  <si>
+    <t>https://transparencia-ciudadana.scjn.gob.mx/resoluciones-relevantes-de-la-SCJN/derechos-digitales/ad-6-2025</t>
+  </si>
+  <si>
+    <t>https://zitacuaro.tecnm.mx/pdf/slider/documento6280.pdf</t>
+  </si>
+  <si>
+    <t>http://dies8.edu.mx/computacionales.htm</t>
+  </si>
+  <si>
+    <t>https://www.unadmexico.mx/nosotros/normatividad</t>
+  </si>
+  <si>
+    <t>https://repositorio.cetys.mx/handle/60000/1925</t>
+  </si>
+  <si>
+    <t>https://www.gaceta.unam.mx/wp-content/uploads/2026/03/260317.pdf</t>
+  </si>
+  <si>
+    <t>Establece los 'Lineamientos Éticos para el Uso Responsable de la Inteligencia Artificial' en la UNACH, fundamentándose en la 'Ley General de Educación Superior' y la 'Ley de Ciencia, Tecnología e Innovación'. Promueve un enfoque institucional basado en riesgos para la gobernanza de la IA en sus funciones académicas y administrativas.</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para la citación de 'contenido desarrollado con inteligencia artificial generativa' y 'figuras elaboradas con herramientas de inteligencia artificial'. Proporciona directrices para la escritura académica en el contexto educativo, promoviendo la claridad y rigor en la presentación de trabajos.</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para el uso de herramientas de 'inteligencia artificial' en CETYS Universidad. Proporciona un marco de referencia para la alfabetización en IA en el contexto educativo.</t>
+  </si>
+  <si>
+    <t>Establece 'Recomendaciones para el uso de Inteligencia Artificial Generativa en la docencia', abordando aspectos como la 'integridad académica' y los 'retos de seguridad'. Proporciona un marco para la implementación reflexiva de IA en entornos educativos.</t>
+  </si>
+  <si>
+    <t>Establece lineamientos relacionados con la 'Inteligencia Artificial' en el contexto educativo. Publicado en el Diario Oficial de la Federación, sugiere un marco normativo para su implementación en el ámbito académico.</t>
+  </si>
+  <si>
+    <t>Establece lineamientos éticos y profesionales para el uso de IA en la producción académica, incluyendo principios como 'Transparencia' y 'Responsabilidad Humana'. Prohíbe la generación de contenido sin intervención humana y exige declaración del uso de herramientas de IA en manuscritos.</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para la 'Maestría en Inteligencia Artificial' y la 'Acreditación de Carreras'. Define aspectos relevantes para la gestión académica en el contexto de la IA.</t>
+  </si>
+  <si>
+    <t>Establece principios éticos fundamentales para la comunidad del IPN, promoviendo la 'honradez', 'justicia' y 'equidad' en el desempeño académico. Aunque no menciona explícitamente la IA, su enfoque en la ética es relevante para la gobernanza de tecnologías emergentes en educación.</t>
+  </si>
+  <si>
+    <t>Establece el propósito de valorar las 'implicaciones éticas' y el 'impacto social' del ejercicio profesional en Ingeniería en Inteligencia Artificial. Incluye contenidos sobre 'ética e ingeniería en inteligencia artificial', lo que lo convierte en un documento relevante para la formación ética en este campo.</t>
+  </si>
+  <si>
+    <t>Establece el 'uso apropiado de la IA' en la UPAEP, alineándose con el Proyecto estratégico RAiSE. Es un marco normativo que guía la implementación de herramientas de IA en el contexto educativo institucional.</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para el uso ético y responsable de la 'Inteligencia Artificial Generativa'. Busca responder a los retos de la era digital en el contexto educativo.</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para el uso de 'Inteligencia Artificial Generativa' en la evaluación educativa, incluyendo 'principios pedagógicos y éticos'. Proporciona recomendaciones sobre aplicaciones y consideraciones éticas en el contexto educativo.</t>
+  </si>
+  <si>
+    <t>Establece que los 'sistemas de alto riesgo' en IA deben cumplir con regulaciones específicas. Define criterios y tópicos relevantes para la evaluación de riesgos en el uso de IA en México.</t>
+  </si>
+  <si>
+    <t>Establece orientaciones sobre el uso de la inteligencia artificial en la Universidad, considerando principios rectores como 'calidad e integridad académica'. Relevante para la regulación del uso de IA en el ámbito académico institucional.</t>
+  </si>
+  <si>
+    <t>Establece un plan de estudios para la 'Licenciatura en Ingeniería en Tecnologías de la Información e Innovación Digital', incluyendo competencias específicas en 'Inteligencia Artificial'. Define lineamientos para la formación profesional en el uso de tecnologías de IA en el sector productivo.</t>
+  </si>
+  <si>
+    <t>Establece que el derecho de autor solo se puede reconocer a las 'personas físicas' y considera que las obras generadas por IA deben ser consideradas como 'productos del dominio público'. Además, menciona que la regulación de la propiedad intelectual varía entre países.</t>
+  </si>
+  <si>
+    <t>Promueve el desarrollo de competencias en 'programación', 'electrónica' e 'inteligencia artificial'. Establece iniciativas para fortalecer vocaciones en STEM y vincular el aprendizaje científico con eventos sociales como el Mundial de Fútbol 2026.</t>
+  </si>
+  <si>
+    <t>Establece la 'dirección de proyectos de investigación' en el campo de la inteligencia artificial, aplicados a la solución de problemas específicos. Regula la utilización de sistemas de cómputo en este ámbito.</t>
+  </si>
+  <si>
+    <t>Establece directrices para el 'Uso Ético y Responsable de la Inteligencia Artificial' en el ámbito académico. Proporciona un marco normativo que busca regular la implementación de IA en procesos educativos dentro de la institución.</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para el uso ético de la 'inteligencia artificial generativa' en programas de posgrado. Advierte sobre las consecuencias del mal uso en la 'integridad académica'.</t>
+  </si>
+  <si>
+    <t>Establece la creación del 'Consejo Coordinador de Inteligencia Artificial' en la UNAM, con el objetivo de potenciar las capacidades institucionales en IA y fortalecer la autonomía tecnológica de la Universidad.</t>
+  </si>
+  <si>
+    <t>Protección de datos</t>
+  </si>
+  <si>
+    <t>Lineamiento académico</t>
+  </si>
+  <si>
+    <t>Guía pedagógica</t>
+  </si>
+  <si>
+    <t>Código de ética</t>
+  </si>
+  <si>
+    <t>Resolución</t>
+  </si>
+  <si>
+    <t>Estrategia nacional</t>
   </si>
 </sst>
 </file>
@@ -1170,7 +1420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1196,6 +1446,7 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1502,7 +1753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.1796875" customWidth="1"/>
@@ -4062,8 +4313,12 @@
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
+      <c r="A63" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="C63" s="3" t="s">
         <v>312</v>
       </c>
@@ -4099,8 +4354,12 @@
       </c>
     </row>
     <row r="64" spans="1:13" ht="58" x14ac:dyDescent="0.35">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
+      <c r="A64" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="C64" s="3" t="s">
         <v>317</v>
       </c>
@@ -4136,8 +4395,12 @@
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
+      <c r="A65" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="C65" s="3" t="s">
         <v>321</v>
       </c>
@@ -4173,8 +4436,12 @@
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
+      <c r="A66" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="C66" s="3" t="s">
         <v>326</v>
       </c>
@@ -4210,8 +4477,12 @@
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
+      <c r="A67" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="C67" s="3" t="s">
         <v>329</v>
       </c>
@@ -4247,8 +4518,12 @@
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
+      <c r="A68" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="C68" s="3" t="s">
         <v>334</v>
       </c>
@@ -4284,94 +4559,1194 @@
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
+      <c r="A69" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J69" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="3"/>
-      <c r="L70" s="3"/>
-      <c r="M70" s="3"/>
+      <c r="A70" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="3"/>
-      <c r="L71" s="3"/>
-      <c r="M71" s="3"/>
+      <c r="A71" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="M71" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="3"/>
-      <c r="L72" s="3"/>
-      <c r="M72" s="3"/>
+      <c r="A72" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
+      <c r="A73" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
+      <c r="A74" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J74" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="M74" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A75" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="M75" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A76" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A77" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J77" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A78" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A79" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A80" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J80" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A81" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="6">
+        <v>2025</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A82" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="M82" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A83" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A84" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J84" s="6">
+        <v>45663</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="L84" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M84" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A85" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="L85" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="M85" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A86" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J86" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="L86" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A87" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J87" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="M87" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A88" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J88" s="6">
+        <v>2025</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="M88" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A89" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="3"/>
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="6"/>
+      <c r="K91" s="3"/>
+      <c r="L91" s="3"/>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="6"/>
+      <c r="K92" s="3"/>
+      <c r="L92" s="11"/>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="3"/>
+      <c r="J93" s="6"/>
+      <c r="K93" s="3"/>
+      <c r="L93" s="3"/>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="3"/>
+      <c r="L94" s="3"/>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="6"/>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="6"/>
+      <c r="K96" s="3"/>
+      <c r="L96" s="3"/>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="6"/>
+      <c r="K97" s="3"/>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="3"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="3"/>
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3"/>
+      <c r="J101" s="6"/>
+      <c r="K101" s="3"/>
+      <c r="L101" s="3"/>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="6"/>
+      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="6"/>
+      <c r="K103" s="3"/>
+      <c r="L103" s="3"/>
+      <c r="M103" s="3"/>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3"/>
+      <c r="J104" s="6"/>
+      <c r="K104" s="3"/>
+      <c r="L104" s="3"/>
+      <c r="M104" s="3"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="3"/>
+      <c r="J105" s="6"/>
+      <c r="K105" s="3"/>
+      <c r="L105" s="3"/>
+      <c r="M105" s="3"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A106" s="3"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
+      <c r="J106" s="6"/>
+      <c r="K106" s="3"/>
+      <c r="L106" s="3"/>
+      <c r="M106" s="3"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3"/>
+      <c r="J107" s="6"/>
+      <c r="K107" s="3"/>
+      <c r="L107" s="3"/>
+      <c r="M107" s="3"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3"/>
+      <c r="J108" s="6"/>
+      <c r="K108" s="3"/>
+      <c r="L108" s="3"/>
+      <c r="M108" s="3"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="3"/>
+      <c r="L109" s="3"/>
+      <c r="M109" s="3"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
+      <c r="J110" s="6"/>
+      <c r="K110" s="3"/>
+      <c r="L110" s="3"/>
+      <c r="M110" s="3"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="3"/>
+      <c r="J111" s="6"/>
+      <c r="K111" s="3"/>
+      <c r="L111" s="3"/>
+      <c r="M111" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -4422,7 +5797,7 @@
           <x14:formula1>
             <xm:f>'Vinculo con educacion'!$A$1:$A$2</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H1048576</xm:sqref>
+          <xm:sqref>H91:H1048576 H2:H89</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
